--- a/4 External Data/Massachusetts 2050 Decarbonization Roadmap Study/Figure 62 - Report.xlsx
+++ b/4 External Data/Massachusetts 2050 Decarbonization Roadmap Study/Figure 62 - Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amirgazar/Documents/GitHub/Decarbonization-Tradeoffs/4 External Data/Massachusetts 2050 Decarbonization Roadmap Study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amirgazar/Documents/GitHub/Decarbonization-Tradeoffs R1.v.2/4 External Data/Massachusetts 2050 Decarbonization Roadmap Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF904881-FCFE-FD47-8D18-2CF8BC873078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F69B67-2E2F-A043-B100-D88C3C64C177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{57CF73A6-EFC2-734A-A588-22BF54CAE4D9}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17220" xr2:uid="{57CF73A6-EFC2-734A-A588-22BF54CAE4D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Original table" sheetId="1" r:id="rId1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
-  <si>
-    <t xml:space="preserve">Table 23 Gross Massachusetts energy system cost (2018$B) by category in 2050 for each pathway </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>Cost Group</t>
   </si>
@@ -654,42 +651,42 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
@@ -724,7 +721,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="5">
         <v>0.16</v>
@@ -733,7 +730,7 @@
         <v>0.25</v>
       </c>
       <c r="D3" s="14">
-        <f t="shared" ref="D3:D18" si="0">C3*1.23375</f>
+        <f t="shared" ref="D3:D17" si="0">C3*1.23375</f>
         <v>0.30843749999999998</v>
       </c>
       <c r="E3" s="5">
@@ -760,7 +757,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5">
         <v>3.29</v>
@@ -795,7 +792,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5">
         <v>1.71</v>
@@ -831,7 +828,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="5">
         <v>2.64</v>
@@ -867,7 +864,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="5">
         <v>0.18</v>
@@ -903,7 +900,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="5">
         <v>0.24</v>
@@ -939,7 +936,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5">
         <v>0.31</v>
@@ -975,7 +972,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="5">
         <v>0.05</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5">
         <v>0.79</v>
@@ -1046,7 +1043,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="5">
         <v>1.03</v>
@@ -1082,7 +1079,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="5">
         <v>0.28999999999999998</v>
@@ -1118,7 +1115,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="5">
         <v>0.01</v>
@@ -1154,7 +1151,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="5">
         <v>0.01</v>
@@ -1190,7 +1187,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="5">
         <v>1.8</v>
@@ -1226,7 +1223,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="5">
         <v>9.1300000000000008</v>
@@ -1262,7 +1259,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5">
         <v>0.71</v>
@@ -1298,7 +1295,7 @@
     </row>
     <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="6">
         <f>SUM(B2:B18)</f>
@@ -1343,7 +1340,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B20" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="16">
         <f>PV(0.02,26,-C19)</f>
@@ -1358,9 +1355,7 @@
       <c r="A21" s="1"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="A22" s="4"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
@@ -1408,13 +1403,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -1426,7 +1421,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5">
         <v>0.16</v>
@@ -1437,7 +1432,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5">
         <v>1.71</v>
@@ -1448,7 +1443,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5">
         <v>0.18</v>
@@ -1457,7 +1452,7 @@
         <v>0.17</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>1.2337499999999999</v>
@@ -1465,7 +1460,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5">
         <v>0.31</v>
@@ -1476,7 +1471,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="5">
         <v>0.05</v>
@@ -1487,7 +1482,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="5">
         <v>1.03</v>
@@ -1498,7 +1493,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="5">
         <v>0.28999999999999998</v>
@@ -1509,7 +1504,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5">
         <v>1.8</v>
@@ -1520,7 +1515,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="5">
         <v>9.1300000000000008</v>
@@ -1531,7 +1526,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="5">
         <v>0.71</v>
@@ -1542,7 +1537,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="6">
         <f>SUM(B2:B11)</f>
@@ -1562,7 +1557,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="7">
         <f>B12*F4</f>
@@ -1576,7 +1571,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="12">
         <f>PV(0.03,26,-C13)</f>
@@ -1599,10 +1594,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
         <v>31</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
